--- a/historicoresultadosloteriasnacionais/mega_sena_asloterias_ate_concurso_3029_crescente.xlsx
+++ b/historicoresultadosloteriasnacionais/mega_sena_asloterias_ate_concurso_3029_crescente.xlsx
@@ -3648,6 +3648,11 @@
       <c r="A3083" t="n">
         <v>2</v>
       </c>
+      <c r="B3083" t="inlineStr">
+        <is>
+          <t>1996-03-18</t>
+        </is>
+      </c>
       <c r="C3083" t="inlineStr">
         <is>
           <t>09</t>
@@ -3711,6 +3716,11 @@
       <c r="A3085" t="n">
         <v>3</v>
       </c>
+      <c r="B3085" t="inlineStr">
+        <is>
+          <t>1996-03-25</t>
+        </is>
+      </c>
       <c r="C3085" t="inlineStr">
         <is>
           <t>10</t>
@@ -3774,6 +3784,11 @@
       <c r="A3087" t="n">
         <v>4</v>
       </c>
+      <c r="B3087" t="inlineStr">
+        <is>
+          <t>1996-04-01</t>
+        </is>
+      </c>
       <c r="C3087" t="inlineStr">
         <is>
           <t>01</t>
@@ -3837,6 +3852,11 @@
       <c r="A3089" t="n">
         <v>5</v>
       </c>
+      <c r="B3089" t="inlineStr">
+        <is>
+          <t>1996-04-08</t>
+        </is>
+      </c>
       <c r="C3089" t="inlineStr">
         <is>
           <t>01</t>
@@ -3900,6 +3920,11 @@
       <c r="A3091" t="n">
         <v>6</v>
       </c>
+      <c r="B3091" t="inlineStr">
+        <is>
+          <t>1996-04-15</t>
+        </is>
+      </c>
       <c r="C3091" t="inlineStr">
         <is>
           <t>07</t>
@@ -4026,6 +4051,11 @@
       <c r="A3095" t="n">
         <v>8</v>
       </c>
+      <c r="B3095" t="inlineStr">
+        <is>
+          <t>1996-04-29</t>
+        </is>
+      </c>
       <c r="C3095" t="inlineStr">
         <is>
           <t>04</t>
@@ -4089,6 +4119,11 @@
       <c r="A3097" t="n">
         <v>9</v>
       </c>
+      <c r="B3097" t="inlineStr">
+        <is>
+          <t>1996-05-06</t>
+        </is>
+      </c>
       <c r="C3097" t="inlineStr">
         <is>
           <t>08</t>
@@ -4152,6 +4187,11 @@
       <c r="A3099" t="n">
         <v>10</v>
       </c>
+      <c r="B3099" t="inlineStr">
+        <is>
+          <t>1996-05-13</t>
+        </is>
+      </c>
       <c r="C3099" t="inlineStr">
         <is>
           <t>04</t>
@@ -4215,6 +4255,11 @@
       <c r="A3101" t="n">
         <v>11</v>
       </c>
+      <c r="B3101" t="inlineStr">
+        <is>
+          <t>1996-05-20</t>
+        </is>
+      </c>
       <c r="C3101" t="inlineStr">
         <is>
           <t>15</t>
@@ -4278,6 +4323,11 @@
       <c r="A3103" t="n">
         <v>12</v>
       </c>
+      <c r="B3103" t="inlineStr">
+        <is>
+          <t>1996-05-27</t>
+        </is>
+      </c>
       <c r="C3103" t="inlineStr">
         <is>
           <t>04</t>
@@ -4341,6 +4391,11 @@
       <c r="A3105" t="n">
         <v>13</v>
       </c>
+      <c r="B3105" t="inlineStr">
+        <is>
+          <t>1996-06-03</t>
+        </is>
+      </c>
       <c r="C3105" t="inlineStr">
         <is>
           <t>18</t>
@@ -4404,6 +4459,11 @@
       <c r="A3107" t="n">
         <v>14</v>
       </c>
+      <c r="B3107" t="inlineStr">
+        <is>
+          <t>1996-06-10</t>
+        </is>
+      </c>
       <c r="C3107" t="inlineStr">
         <is>
           <t>02</t>
@@ -4467,6 +4527,11 @@
       <c r="A3109" t="n">
         <v>15</v>
       </c>
+      <c r="B3109" t="inlineStr">
+        <is>
+          <t>1996-06-17</t>
+        </is>
+      </c>
       <c r="C3109" t="inlineStr">
         <is>
           <t>12</t>
@@ -4530,6 +4595,11 @@
       <c r="A3111" t="n">
         <v>16</v>
       </c>
+      <c r="B3111" t="inlineStr">
+        <is>
+          <t>1996-06-24</t>
+        </is>
+      </c>
       <c r="C3111" t="inlineStr">
         <is>
           <t>20</t>
@@ -4719,6 +4789,11 @@
       <c r="A3117" t="n">
         <v>19</v>
       </c>
+      <c r="B3117" t="inlineStr">
+        <is>
+          <t>1996-07-15</t>
+        </is>
+      </c>
       <c r="C3117" t="inlineStr">
         <is>
           <t>05</t>
@@ -4782,6 +4857,11 @@
       <c r="A3119" t="n">
         <v>20</v>
       </c>
+      <c r="B3119" t="inlineStr">
+        <is>
+          <t>1996-07-22</t>
+        </is>
+      </c>
       <c r="C3119" t="inlineStr">
         <is>
           <t>11</t>
@@ -4845,6 +4925,11 @@
       <c r="A3121" t="n">
         <v>21</v>
       </c>
+      <c r="B3121" t="inlineStr">
+        <is>
+          <t>1996-07-29</t>
+        </is>
+      </c>
       <c r="C3121" t="inlineStr">
         <is>
           <t>06</t>
@@ -89440,6 +89525,11 @@
       <c r="A6142" t="n">
         <v>3042</v>
       </c>
+      <c r="B6142" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
       <c r="C6142" t="inlineStr">
         <is>
           <t>02</t>
@@ -89475,6 +89565,11 @@
       <c r="A6143" t="n">
         <v>3043</v>
       </c>
+      <c r="B6143" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="C6143" t="inlineStr">
         <is>
           <t>10</t>
@@ -89545,6 +89640,11 @@
       <c r="A6145" t="n">
         <v>3045</v>
       </c>
+      <c r="B6145" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
       <c r="C6145" t="inlineStr">
         <is>
           <t>23</t>
@@ -89580,6 +89680,11 @@
       <c r="A6146" t="n">
         <v>3046</v>
       </c>
+      <c r="B6146" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="C6146" t="inlineStr">
         <is>
           <t>16</t>
@@ -89614,6 +89719,11 @@
     <row r="6147">
       <c r="A6147" t="n">
         <v>3047</v>
+      </c>
+      <c r="B6147" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
       </c>
       <c r="C6147" t="inlineStr">
         <is>
